--- a/external-data-scraper/AcademicCalendars/UERM_MSC_AcademicCalendar.xlsx
+++ b/external-data-scraper/AcademicCalendars/UERM_MSC_AcademicCalendar.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,45 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>academic_calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>external_acad_cal_0001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V. Mapa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UERM Medicine Student Council</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/UERMMSC/posts/pfbid0zeAdYsz6tbqU79fPt5RGn1sGEmDR9VPsXsrYrexR9hZ67bSWN1MfcPF95cBfqvCjl?ref=embed_page</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-06-26T10:43:54.798771+00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-21T10:43:54.798771+00:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>academic_calendar</t>
         </is>
